--- a/pipeline/credit_rating/output/fiinratings_xhtn_20261029.xlsx
+++ b/pipeline/credit_rating/output/fiinratings_xhtn_20261029.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O2" s="1" t="n">
@@ -624,7 +624,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O3" s="1" t="n">
@@ -695,7 +695,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O4" s="1" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O5" s="1" t="n">
@@ -829,7 +829,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O6" s="1" t="n">
@@ -900,7 +900,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O11" s="1" t="n">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O12" s="1" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O13" s="1" t="n">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O14" s="1" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O15" s="1" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O17" s="1" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O18" s="1" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O19" s="1" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O20" s="1" t="n">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O21" s="1" t="n">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O22" s="1" t="n">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O23" s="1" t="n">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O24" s="1" t="n">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O25" s="1" t="n">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O26" s="1" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O27" s="1" t="n">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O28" s="1" t="n">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O29" s="1" t="n">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O30" s="1" t="n">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O31" s="1" t="n">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O32" s="1" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O33" s="1" t="n">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O34" s="1" t="n">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O35" s="1" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O36" s="1" t="n">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O37" s="1" t="n">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O39" s="1" t="n">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O41" s="1" t="n">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O42" s="1" t="n">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O44" s="1" t="n">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O45" s="1" t="n">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O47" s="1" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O48" s="1" t="n">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O49" s="1" t="n">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O50" s="1" t="n">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O51" s="1" t="n">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O52" s="1" t="n">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O53" s="1" t="n">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O54" s="1" t="n">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O55" s="1" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O56" s="1" t="n">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O57" s="1" t="n">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O58" s="1" t="n">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O60" s="1" t="n">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O61" s="1" t="n">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O62" s="1" t="n">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O63" s="1" t="n">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O64" s="1" t="n">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O65" s="1" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O66" s="1" t="n">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O67" s="1" t="n">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O68" s="1" t="n">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O69" s="1" t="n">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O70" s="1" t="n">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O71" s="1" t="n">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O72" s="1" t="n">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O73" s="1" t="n">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O74" s="1" t="n">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O75" s="1" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O76" s="1" t="n">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O77" s="1" t="n">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O78" s="1" t="n">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O79" s="1" t="n">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O80" s="1" t="n">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O81" s="1" t="n">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O82" s="1" t="n">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O83" s="1" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O84" s="1" t="n">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O85" s="1" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O86" s="1" t="n">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O87" s="1" t="n">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O88" s="1" t="n">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O89" s="1" t="n">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O90" s="1" t="n">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O91" s="1" t="n">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O92" s="1" t="n">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O93" s="1" t="n">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O94" s="1" t="n">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O95" s="1" t="n">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O96" s="1" t="n">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O97" s="1" t="n">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O98" s="1" t="n">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O99" s="1" t="n">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O100" s="1" t="n">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O101" s="1" t="n">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O102" s="1" t="n">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O103" s="1" t="n">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O104" s="1" t="n">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O105" s="1" t="n">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O106" s="1" t="n">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O107" s="1" t="n">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O108" s="1" t="n">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O109" s="1" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O110" s="1" t="n">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O111" s="1" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O112" s="1" t="n">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O113" s="1" t="n">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O114" s="1" t="n">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O115" s="1" t="n">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O116" s="1" t="n">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O117" s="1" t="n">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O118" s="1" t="n">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O119" s="1" t="n">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O120" s="1" t="n">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O121" s="1" t="n">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O122" s="1" t="n">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O123" s="1" t="n">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O124" s="1" t="n">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O125" s="1" t="n">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O126" s="1" t="n">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O127" s="1" t="n">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O128" s="1" t="n">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O129" s="1" t="n">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O130" s="1" t="n">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O131" s="1" t="n">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O132" s="1" t="n">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O133" s="1" t="n">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O134" s="1" t="n">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O135" s="1" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O136" s="1" t="n">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O137" s="1" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O138" s="1" t="n">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O139" s="1" t="n">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O140" s="1" t="n">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O141" s="1" t="n">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O142" s="1" t="n">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O143" s="1" t="n">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O144" s="1" t="n">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O145" s="1" t="n">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O146" s="1" t="n">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O147" s="1" t="n">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O148" s="1" t="n">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O149" s="1" t="n">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O150" s="1" t="n">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O151" s="1" t="n">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O152" s="1" t="n">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O153" s="1" t="n">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O154" s="1" t="n">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O155" s="1" t="n">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O156" s="1" t="n">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O157" s="1" t="n">
@@ -10585,7 +10585,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O158" s="1" t="n">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O159" s="1" t="n">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O160" s="1" t="n">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O161" s="1" t="n">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O162" s="1" t="n">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O163" s="1" t="n">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O164" s="1" t="n">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O165" s="1" t="n">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O166" s="1" t="n">
@@ -11152,7 +11152,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O167" s="1" t="n">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O168" s="1" t="n">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O169" s="1" t="n">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O170" s="1" t="n">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O171" s="1" t="n">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O172" s="1" t="n">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O173" s="1" t="n">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O174" s="1" t="n">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O175" s="1" t="n">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O176" s="1" t="n">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O177" s="1" t="n">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O178" s="1" t="n">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O179" s="1" t="n">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O180" s="1" t="n">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O181" s="1" t="n">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O182" s="1" t="n">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O183" s="1" t="n">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O184" s="1" t="n">
@@ -12286,7 +12286,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O185" s="1" t="n">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O186" s="1" t="n">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O187" s="1" t="n">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O188" s="1" t="n">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O189" s="1" t="n">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O190" s="1" t="n">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O191" s="1" t="n">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O192" s="1" t="n">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O193" s="1" t="n">
@@ -12853,7 +12853,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O194" s="1" t="n">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O195" s="1" t="n">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O196" s="1" t="n">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O197" s="1" t="n">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O198" s="1" t="n">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O199" s="1" t="n">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O200" s="1" t="n">
@@ -13294,7 +13294,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O201" s="1" t="n">
@@ -13357,7 +13357,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O202" s="1" t="n">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O203" s="1" t="n">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:40</t>
+          <t>2026-10-29 15:27:50</t>
         </is>
       </c>
       <c r="O204" s="1" t="n">
